--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260615.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260615.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>26.96%</t>
+          <t>26.98%</t>
         </is>
       </c>
     </row>
@@ -638,51 +638,51 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.42%</t>
+          <t>9.57%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>GEV US</t>
+          <t>MRVL US</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>奇異維諾瓦公司</t>
+          <t>Marvell Technology Inc</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>18,575</t>
+          <t>60,105</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.56%</t>
+          <t>7.81%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>MRVL US</t>
+          <t>GEV US</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Marvell Technology Inc</t>
+          <t>奇異維諾瓦公司</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>60,105</t>
+          <t>18,575</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.28%</t>
+          <t>7.65%</t>
         </is>
       </c>
     </row>
@@ -704,29 +704,29 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.34%</t>
+          <t>5.19%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>NOW US</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>ServiceNow Inc</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>267,442,084</t>
+          <t>70,230</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.66%</t>
+          <t>3.08%</t>
         </is>
       </c>
     </row>
@@ -748,139 +748,139 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.15%</t>
+          <t>3.05%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>NOW US</t>
+          <t>EQIX US</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>ServiceNow Inc</t>
+          <t>Equinix公司</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>70,230</t>
+          <t>6,765</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.11%</t>
+          <t>3.03%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>EQIX US</t>
+          <t>DUK US</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Equinix公司</t>
+          <t>杜克能源公司</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>6,765</t>
+          <t>53,355</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.09%</t>
+          <t>2.81%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>DUK US</t>
+          <t>CEG US</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>杜克能源公司</t>
+          <t>星座能源公司</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>53,355</t>
+          <t>23,335</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.89%</t>
+          <t>2.57%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>CEG US</t>
+          <t>NET US</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>星座能源公司</t>
+          <t>Cloudflare公司</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>23,335</t>
+          <t>21,583</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.56%</t>
+          <t>2.14%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>NET US</t>
+          <t>AEP US</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Cloudflare公司</t>
+          <t>美國電力公司</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>21,583</t>
+          <t>37,250</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>2.03%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>AEP US</t>
+          <t>HPE US</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>美國電力公司</t>
+          <t>慧與</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>37,250</t>
+          <t>90,915</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>1.87%</t>
         </is>
       </c>
     </row>
@@ -902,68 +902,68 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>1.86%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>HPE US</t>
+          <t>D US</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>慧與</t>
+          <t>道明尼能源公司</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>90,915</t>
+          <t>60,305</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.90%</t>
+          <t>1.73%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>D US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>道明尼能源公司</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>60,305</t>
+          <t>9,440</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.77%</t>
+          <t>1.55%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>NBIS US</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>尼比厄斯集團公眾有限公司</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>31,398</t>
+          <t>13,831</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -975,44 +975,44 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>9,440</t>
+          <t>23,040</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.49%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>23,040</t>
+          <t>31,398</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.47%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.43%</t>
         </is>
       </c>
     </row>
@@ -1056,227 +1056,227 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.36%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>NBIS US</t>
+          <t>CRDO US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>尼比厄斯集團公眾有限公司</t>
+          <t>Credo科技集團控股有限公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>13,831</t>
+          <t>11,376</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.24%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>CRDO US</t>
+          <t>ED US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Credo科技集團控股有限公司</t>
+          <t>聯合愛迪生</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>11,376</t>
+          <t>25,228</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.14%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>ED US</t>
+          <t>CRWV US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>聯合愛迪生</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>25,228</t>
+          <t>23,307</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>149,895</t>
+          <t>21,865</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>21,865</t>
+          <t>149,895</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>CRWV US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>23,307</t>
+          <t>18,871</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>18,871</t>
+          <t>44,340</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.80%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>PPL Corp</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>44,340</t>
+          <t>51,070</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.78%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>PPL Corp</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>51,070</t>
+          <t>14,015</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.77%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>14,015</t>
+          <t>49,473,340</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.66%</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.55%</t>
         </is>
       </c>
     </row>
